--- a/testData/E2E_UAT_022_Part_2.xlsx
+++ b/testData/E2E_UAT_022_Part_2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation_Project\E2E_Automation\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netapp-my.sharepoint.com/personal/sunilr2_netapp_com/Documents/Desktop/Playwright Python/E2E_Automation/testData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F914FA4C-3E60-41C9-9E88-83FF387A3184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{F914FA4C-3E60-41C9-9E88-83FF387A3184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B8A3D9A-E3DE-4CAE-9B6D-B8C4043E19CA}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="21600" windowHeight="13749" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -105,9 +105,6 @@
     <t>Test for Automation</t>
   </si>
   <si>
-    <t>To be Determined Before Qualify Sales Stage</t>
-  </si>
-  <si>
     <t>Up-sell/Cross-sell</t>
   </si>
   <si>
@@ -165,9 +162,6 @@
     <t>Reseller</t>
   </si>
   <si>
-    <t>Rajwesh Smam</t>
-  </si>
-  <si>
     <t>Reseller through Distributor</t>
   </si>
   <si>
@@ -231,15 +225,9 @@
     <t>Encryption_Storage</t>
   </si>
   <si>
-    <t>FIPS</t>
-  </si>
-  <si>
     <t>Capacity_Storage</t>
   </si>
   <si>
-    <t>10TB</t>
-  </si>
-  <si>
     <t>Qty Per Enclosure_Storage</t>
   </si>
   <si>
@@ -343,6 +331,18 @@
   </si>
   <si>
     <t>Distributor</t>
+  </si>
+  <si>
+    <t>test test</t>
+  </si>
+  <si>
+    <t>To be Determined at Qualify Sales Stage</t>
+  </si>
+  <si>
+    <t>Non-FDE</t>
+  </si>
+  <si>
+    <t>4TB</t>
   </si>
 </sst>
 </file>
@@ -497,12 +497,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -519,6 +513,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -859,143 +859,143 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="15.9" x14ac:dyDescent="0.45">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="17"/>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="17"/>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="17"/>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
-      <c r="AS1" s="17"/>
-      <c r="AT1" s="17"/>
-      <c r="AU1" s="17"/>
-      <c r="AV1" s="17"/>
-      <c r="AW1" s="17"/>
-      <c r="AX1" s="17"/>
-      <c r="AY1" s="17"/>
-      <c r="AZ1" s="17"/>
-      <c r="BA1" s="18"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15"/>
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15"/>
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15"/>
+      <c r="AO1" s="15"/>
+      <c r="AP1" s="15"/>
+      <c r="AQ1" s="15"/>
+      <c r="AR1" s="15"/>
+      <c r="AS1" s="15"/>
+      <c r="AT1" s="15"/>
+      <c r="AU1" s="15"/>
+      <c r="AV1" s="15"/>
+      <c r="AW1" s="15"/>
+      <c r="AX1" s="15"/>
+      <c r="AY1" s="15"/>
+      <c r="AZ1" s="15"/>
+      <c r="BA1" s="16"/>
       <c r="BB1" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
       <c r="R2" s="2"/>
-      <c r="S2" s="11" t="s">
+      <c r="S2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="V2" s="11"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
-      <c r="AA2" s="11"/>
-      <c r="AB2" s="11"/>
-      <c r="AC2" s="11"/>
-      <c r="AD2" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="AE2" s="11"/>
-      <c r="AF2" s="11"/>
-      <c r="AG2" s="11"/>
-      <c r="AH2" s="11"/>
-      <c r="AI2" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ2" s="11"/>
-      <c r="AK2" s="11"/>
-      <c r="AL2" s="11"/>
-      <c r="AM2" s="11"/>
-      <c r="AN2" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="AO2" s="11"/>
-      <c r="AP2" s="11"/>
-      <c r="AQ2" s="11"/>
-      <c r="AR2" s="11"/>
-      <c r="AS2" s="11"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="V2" s="17"/>
+      <c r="W2" s="17"/>
+      <c r="X2" s="17"/>
+      <c r="Y2" s="17"/>
+      <c r="Z2" s="17"/>
+      <c r="AA2" s="17"/>
+      <c r="AB2" s="17"/>
+      <c r="AC2" s="17"/>
+      <c r="AD2" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE2" s="17"/>
+      <c r="AF2" s="17"/>
+      <c r="AG2" s="17"/>
+      <c r="AH2" s="17"/>
+      <c r="AI2" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ2" s="17"/>
+      <c r="AK2" s="17"/>
+      <c r="AL2" s="17"/>
+      <c r="AM2" s="17"/>
+      <c r="AN2" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="AO2" s="17"/>
+      <c r="AP2" s="17"/>
+      <c r="AQ2" s="17"/>
+      <c r="AR2" s="17"/>
+      <c r="AS2" s="17"/>
       <c r="AT2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AU2" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="AV2" s="11"/>
-      <c r="AW2" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="AX2" s="14"/>
-      <c r="AY2" s="14"/>
-      <c r="AZ2" s="14"/>
-      <c r="BA2" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="AU2" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="AV2" s="17"/>
+      <c r="AW2" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX2" s="12"/>
+      <c r="AY2" s="12"/>
+      <c r="AZ2" s="12"/>
+      <c r="BA2" s="13"/>
       <c r="BB2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:54" x14ac:dyDescent="0.4">
@@ -1051,7 +1051,7 @@
         <v>20</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>21</v>
@@ -1060,106 +1060,106 @@
         <v>22</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="V3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="W3" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="X3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="X3" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="Y3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="Z3" s="3" t="s">
+      <c r="AB3" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AA3" s="3" t="s">
+      <c r="AC3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="AB3" s="3" t="s">
+      <c r="AD3" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AC3" s="3" t="s">
+      <c r="AE3" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF3" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AG3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH3" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AE3" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF3" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AG3" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH3" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="AI3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ3" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="AJ3" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="AK3" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AL3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AN3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AP3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AQ3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AT3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AU3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AV3" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="AM3" s="3" t="s">
+      <c r="AW3" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="AN3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="AO3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AP3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AQ3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AS3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AT3" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AU3" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AV3" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="AW3" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="AX3" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="AY3" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="AZ3" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="BA3" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="BB3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.4">
@@ -1176,144 +1176,144 @@
         <v>25</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H4" s="9">
         <v>6121715</v>
       </c>
       <c r="I4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>28</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>29</v>
       </c>
       <c r="L4" s="8"/>
       <c r="M4" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O4" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="S4" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>31</v>
       </c>
       <c r="T4" s="6">
         <v>1000</v>
       </c>
       <c r="U4" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="V4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="W4" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="W4" s="5" t="s">
+      <c r="X4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="X4" s="5" t="s">
-        <v>64</v>
-      </c>
       <c r="Y4" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="Z4" s="5" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="AA4" s="5" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="AB4" s="6">
         <v>6</v>
       </c>
       <c r="AC4" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="AD4" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AE4" s="5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AF4" s="6">
         <v>100</v>
       </c>
       <c r="AG4" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AH4" s="6">
         <v>12</v>
       </c>
       <c r="AI4" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ4" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK4" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL4" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="AJ4" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="AK4" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL4" s="6" t="s">
-        <v>88</v>
       </c>
       <c r="AM4" s="6">
         <v>6</v>
       </c>
       <c r="AN4" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AO4" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AP4" s="5"/>
       <c r="AQ4" s="5"/>
       <c r="AR4" s="5"/>
       <c r="AS4" s="5"/>
       <c r="AT4" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AU4" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="AV4" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AW4" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AX4" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AY4" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="AZ4" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="BA4" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="BB4" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
